--- a/taskflow-task-template_1.xlsx
+++ b/taskflow-task-template_1.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="514">
   <si>
     <t>Title*</t>
   </si>
@@ -1553,6 +1553,60 @@
   </si>
   <si>
     <t>Completed 24 Aug 2026. Restored lost local work from reflog commit 8eda96b / recovery-branch. Merged onto new_crm_rentfoxxy as 6a06758, keeping later customer-refuse commits. Not pushed.</t>
+  </si>
+  <si>
+    <t>TTSPL History drawer — customer name + clickable DC / SO / ticket</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. History drawer now shows customer (or last customer), phone, and email. DC, SO, and support ticket numbers are links to those CRM pages.</t>
+  </si>
+  <si>
+    <t>TTSPL5134 — last customer instead of null after return</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. Returned units cleared current_customer_id so history showed null. Drawer now loads last delivery: Truetech, DC/26-27/1158, SO/26-27/1203, labeled Last customer.</t>
+  </si>
+  <si>
+    <t>Hide extra section on TTSPL History drawer</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. Removed the extra history section the user asked to drop. Customer card and clickable DC/SO/ticket stay.</t>
+  </si>
+  <si>
+    <t>TTSPL5179 — backfill delivery so support ticket can be created</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. Form blocked rented Sleep Management unit because delivered_at and DC were empty. Backfilled from DC-003782 (25 Apr, SO-003887). Ticket create is allowed again.</t>
+  </si>
+  <si>
+    <t>Chandan warehouse lead — lead tools only on assigned tickets</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. chandan@rentfoxxy.com is warehouse lead, not a technician. Support lead assigns tickets/requests to him. He sees My tickets + Resolved, and can run lead actions only on tickets assigned to him. Not in pickup/field tech lists.</t>
+  </si>
+  <si>
+    <t>Return DC — export in-transit laptops with location</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. Added Export in-transit laptops on /sales-pipeline/return-dc. Excel includes TTSPL, serial, customer, city/state/address, current location, courier/AWB, assignee, RDC.</t>
+  </si>
+  <si>
+    <t>TTSPL7547 — support form blocked (reserved leftover Service DC)</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. Khelo Tech form error: reserved, not in customer bucket. Ticket #2927 already replaced it with TTSPL7340 (delivered 21 Aug). Leftover pending SDC/26-27/0003 kept 7547 reserved. Customer should raise on TTSPL7340.</t>
+  </si>
+  <si>
+    <t>List all laptops blocked from creating a support ticket</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. Live scan: 48 units linked to a customer but not rented/on_demo/sold. Reserved 2 (7547, 7654), in transit 15, in repair 1, in stock 5, returned 20, scrapped 5.</t>
+  </si>
+  <si>
+    <t>TTSPL6751 tracking — CRM already received vs physical receive today</t>
+  </si>
+  <si>
+    <t>Completed 26 Aug 2026. Certification Education Providers replacement T-2312 / RDC001664. Pickup stamped warehouse_received 17 Jul 20:36 UTC (no e-sign, no floor ticket). Serial still rented on DC-002131. Replacement TTSPL6842 already delivered. Physical box arrived 26 Aug; CRM looked received because of the false July stamp.</t>
   </si>
 </sst>
 </file>
@@ -1980,27 +2034,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="B2" t="s">
         <v>89</v>
       </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
       <c r="D2" s="3">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="E2" s="2">
-        <v>0.70833333333333337</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>467</v>
       </c>
+      <c r="H2" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="B3" t="s">
         <v>89</v>
@@ -2009,36 +2069,36 @@
         <v>56</v>
       </c>
       <c r="D3" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E3" s="2">
-        <v>0.45833333333333331</v>
+        <v>0.45555555555555555</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
         <v>467</v>
       </c>
       <c r="H3" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="B4" t="s">
         <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D4" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E4" s="2">
-        <v>0.4861111111111111</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -2047,50 +2107,50 @@
         <v>467</v>
       </c>
       <c r="H4" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="B5" t="s">
         <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E5" s="2">
-        <v>0.5</v>
+        <v>0.5111111111111112</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
         <v>467</v>
       </c>
       <c r="H5" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="B6" t="s">
         <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E6" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.5263888888888889</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -2099,24 +2159,24 @@
         <v>467</v>
       </c>
       <c r="H6" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="B7" t="s">
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D7" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E7" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.5361111111111111</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -2125,24 +2185,24 @@
         <v>467</v>
       </c>
       <c r="H7" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="B8" t="s">
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E8" s="2">
-        <v>0.58333333333333337</v>
+        <v>0.6506944444444445</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
@@ -2151,50 +2211,50 @@
         <v>467</v>
       </c>
       <c r="H8" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="B9" t="s">
         <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D9" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E9" s="2">
-        <v>0.625</v>
+        <v>0.6687500000000001</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>467</v>
       </c>
       <c r="H9" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="B10" t="s">
         <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D10" s="3">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="E10" s="2">
-        <v>0.66666666666666663</v>
+        <v>0.7270833333333333</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -2203,164 +2263,32 @@
         <v>467</v>
       </c>
       <c r="H10" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>484</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="3">
-        <v>46258</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.74305555555555547</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" t="s">
-        <v>467</v>
-      </c>
-      <c r="H11" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>486</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="3">
-        <v>46258</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>467</v>
-      </c>
-      <c r="H12" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>488</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="3">
-        <v>46258</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" t="s">
-        <v>467</v>
-      </c>
-      <c r="H13" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>490</v>
-      </c>
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="3">
-        <v>46258</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.76388888888888884</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>467</v>
-      </c>
-      <c r="H14" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>492</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="3">
-        <v>46258</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" t="s">
-        <v>467</v>
-      </c>
-      <c r="H15" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>494</v>
-      </c>
-      <c r="B16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="3">
-        <v>46258</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" t="s">
-        <v>467</v>
-      </c>
-      <c r="H16" t="s">
-        <v>495</v>
-      </c>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="11" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D11" s="3"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D13" s="3"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D14" s="3"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="4:11" x14ac:dyDescent="0.3">
       <c r="D17" s="3"/>
